--- a/常见的系统(设备)默认口令收集.xlsx
+++ b/常见的系统(设备)默认口令收集.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="376">
   <si>
     <t>常见的系统/设备默认口令收集</t>
   </si>
@@ -1137,6 +1137,24 @@
   </si>
   <si>
     <t>admin@localhost</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>circutor</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>为知笔记</t>
+  </si>
+  <si>
+    <t>admin@wiz.cn</t>
+  </si>
+  <si>
+    <t>fofa：title="WizNote"</t>
   </si>
 </sst>
 </file>
@@ -2435,7 +2453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="12" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.44444444444444" style="1" customWidth="1"/>
@@ -5991,6 +6009,46 @@
       </c>
       <c r="F184" s="18"/>
       <c r="G184" s="18"/>
+    </row>
+    <row r="185" ht="15" spans="1:7">
+      <c r="A185" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C185" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D185" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E185" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F185" s="18"/>
+      <c r="G185" s="18"/>
+    </row>
+    <row r="186" ht="15" spans="1:7">
+      <c r="A186" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="B186" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E186" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F186" s="18"/>
+      <c r="G186" s="18" t="s">
+        <v>375</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/常见的系统(设备)默认口令收集.xlsx
+++ b/常见的系统(设备)默认口令收集.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="380">
   <si>
     <t>常见的系统/设备默认口令收集</t>
   </si>
@@ -80,7 +80,7 @@
     <t>管理员</t>
   </si>
   <si>
-    <t>TDengine Management</t>
+    <t>TDengine Management（TDengine 管理系统）</t>
   </si>
   <si>
     <t>root</t>
@@ -1155,6 +1155,18 @@
   </si>
   <si>
     <t>fofa：title="WizNote"</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>博硕BGM 系统</t>
+  </si>
+  <si>
+    <t>Bosure88878181</t>
+  </si>
+  <si>
+    <t>fofa：body="Libs/Platform.lib"</t>
   </si>
 </sst>
 </file>
@@ -2453,7 +2465,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="12" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9.44444444444444" style="1" customWidth="1"/>
@@ -2585,7 +2597,7 @@
       </c>
       <c r="G9" s="18"/>
     </row>
-    <row r="10" ht="15" spans="1:7">
+    <row r="10" ht="30" spans="1:7">
       <c r="A10" s="17">
         <v>2</v>
       </c>
@@ -6048,6 +6060,27 @@
       <c r="F186" s="18"/>
       <c r="G186" s="18" t="s">
         <v>375</v>
+      </c>
+    </row>
+    <row r="187" ht="15" spans="1:7">
+      <c r="A187" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C187" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D187" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="E187" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F187" s="18"/>
+      <c r="G187" s="18" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
